--- a/share/config/orqflow_v0_1/KeySteps.xlsx
+++ b/share/config/orqflow_v0_1/KeySteps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\PyProject\Playwright\OrqFlow_V0.1\share\config\orqflow_v0_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA21409-6D87-416D-B19C-023B733AFE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803329A7-80AD-4FDF-B25F-534C6F603AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
+    <workbookView xWindow="0" yWindow="1020" windowWidth="28800" windowHeight="13395" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/share/config/orqflow_v0_1/KeySteps.xlsx
+++ b/share/config/orqflow_v0_1/KeySteps.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\PyProject\Playwright\OrqFlow_V0.1\share\config\orqflow_v0_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803329A7-80AD-4FDF-B25F-534C6F603AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3E9EF3-DDC2-4E60-8355-200572C17332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1020" windowWidth="28800" windowHeight="13395" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>State</t>
   </si>
@@ -57,23 +57,37 @@
     <t>Moduel</t>
   </si>
   <si>
-    <t>execution_init</t>
-  </si>
-  <si>
     <t>Common</t>
+  </si>
+  <si>
+    <t>PROCESS_TRANSACTION</t>
+  </si>
+  <si>
+    <t>EXECUTION_INIT</t>
+  </si>
+  <si>
+    <t>FRAMEWORK_INIT</t>
+  </si>
+  <si>
+    <t>LOGIN_APPLICATION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,8 +110,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -116,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0DF9C49-C049-4DAE-AD91-7E5CADADA122}" name="Table1" displayName="Table1" ref="A1:G2" totalsRowShown="0">
-  <autoFilter ref="A1:G2" xr:uid="{D0DF9C49-C049-4DAE-AD91-7E5CADADA122}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0DF9C49-C049-4DAE-AD91-7E5CADADA122}" name="Table1" displayName="Table1" ref="A1:G5" totalsRowShown="0">
+  <autoFilter ref="A1:G5" xr:uid="{D0DF9C49-C049-4DAE-AD91-7E5CADADA122}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FE506784-C975-408A-89F3-1CC721EDCF38}" name="Sequence"/>
     <tableColumn id="2" xr3:uid="{95690DC6-D21B-41DA-BE32-03FF3223FB99}" name="Bot"/>
@@ -428,17 +445,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C847CD3D-3E9A-4A0E-8DB4-1E704C084D28}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -461,17 +478,41 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/share/config/orqflow_v0_1/KeySteps.xlsx
+++ b/share/config/orqflow_v0_1/KeySteps.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\PyProject\Playwright\OrqFlow_V0.1\share\config\orqflow_v0_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chargebackgurus-my.sharepoint.com/personal/venkateswaran_krishnan_chargebackgurus_com/Documents/Desktop/Temp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3E9EF3-DDC2-4E60-8355-200572C17332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{3A3E9EF3-DDC2-4E60-8355-200572C17332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{585FC93A-64DE-4C33-8BF9-0C01633A5BD6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1020" windowWidth="28800" windowHeight="13395" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>State</t>
   </si>
@@ -149,9 +149,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +189,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -295,7 +295,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,7 +437,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -499,6 +499,12 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
@@ -507,6 +513,12 @@
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
@@ -514,6 +526,12 @@
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/share/config/orqflow_v0_1/KeySteps.xlsx
+++ b/share/config/orqflow_v0_1/KeySteps.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\PyProject\Playwright\OrqFlow_V0.1\share\config\orqflow_v0_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3E9EF3-DDC2-4E60-8355-200572C17332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CEA4CF-ADAC-4B1E-B628-B2FD63E81C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1020" windowWidth="28800" windowHeight="13395" xr2:uid="{7952E89B-BE15-4916-8DDD-123323AF50EF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>State</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Application</t>
   </si>
   <si>
-    <t>Moduel</t>
-  </si>
-  <si>
     <t>Common</t>
   </si>
   <si>
@@ -70,6 +67,12 @@
   </si>
   <si>
     <t>LOGIN_APPLICATION</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>image_value_extraction.runtime:run_process</t>
   </si>
 </sst>
 </file>
@@ -141,7 +144,7 @@
     <tableColumn id="3" xr3:uid="{FE310E18-126F-4D27-AA9E-E413F3A7A75A}" name="State"/>
     <tableColumn id="4" xr3:uid="{ACF77BA4-8A99-4B9E-A0BA-168C8A2C04A2}" name="BatchCount"/>
     <tableColumn id="5" xr3:uid="{B78F3D85-461B-4B80-BFA3-F79FAFC468DD}" name="Application"/>
-    <tableColumn id="6" xr3:uid="{E68CFF3F-0A88-4EF6-A5F4-6400A233ACCC}" name="Moduel"/>
+    <tableColumn id="6" xr3:uid="{E68CFF3F-0A88-4EF6-A5F4-6400A233ACCC}" name="Module"/>
     <tableColumn id="7" xr3:uid="{0008BBDB-911A-4FCB-94F9-583EBA908E1F}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -472,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -483,13 +486,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -497,7 +500,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -505,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,7 +516,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
